--- a/BWI/bestwine_output/bestwine_Serbia.xlsx
+++ b/BWI/bestwine_output/bestwine_Serbia.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA182"/>
+  <dimension ref="A1:AA183"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -20170,6 +20170,103 @@
       <c r="Z182" s="2" t="inlineStr"/>
       <c r="AA182" s="2" t="inlineStr"/>
     </row>
+    <row r="183">
+      <c r="A183" s="2" t="inlineStr">
+        <is>
+          <t>Dan Company Doo</t>
+        </is>
+      </c>
+      <c r="B183" s="2" t="inlineStr">
+        <is>
+          <t>Dan Company Doo</t>
+        </is>
+      </c>
+      <c r="C183" s="2" t="inlineStr">
+        <is>
+          <t>32642</t>
+        </is>
+      </c>
+      <c r="D183" s="2" t="inlineStr">
+        <is>
+          <t>Serbia</t>
+        </is>
+      </c>
+      <c r="E183" s="2" t="inlineStr">
+        <is>
+          <t>Beograd</t>
+        </is>
+      </c>
+      <c r="F183" s="2" t="inlineStr">
+        <is>
+          <t>Grad Beograd</t>
+        </is>
+      </c>
+      <c r="G183" s="2" t="inlineStr">
+        <is>
+          <t>41 Lomina</t>
+        </is>
+      </c>
+      <c r="H183" s="2" t="inlineStr">
+        <is>
+          <t>11000</t>
+        </is>
+      </c>
+      <c r="I183" s="2" t="inlineStr">
+        <is>
+          <t>https://dan-company.com</t>
+        </is>
+      </c>
+      <c r="J183" s="2" t="inlineStr"/>
+      <c r="K183" s="2" t="inlineStr"/>
+      <c r="L183" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M183" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N183" s="2" t="inlineStr">
+        <is>
+          <t>office@dan-company.com</t>
+        </is>
+      </c>
+      <c r="O183" s="2" t="inlineStr">
+        <is>
+          <t>+381 11 2644148</t>
+        </is>
+      </c>
+      <c r="P183" s="2" t="inlineStr">
+        <is>
+          <t>1992</t>
+        </is>
+      </c>
+      <c r="Q183" s="2" t="inlineStr">
+        <is>
+          <t>06205976</t>
+        </is>
+      </c>
+      <c r="R183" s="2" t="inlineStr"/>
+      <c r="S183" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/vinotekachianti/</t>
+        </is>
+      </c>
+      <c r="T183" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/vinoteka_chianti/</t>
+        </is>
+      </c>
+      <c r="U183" s="2" t="inlineStr"/>
+      <c r="V183" s="2" t="inlineStr"/>
+      <c r="W183" s="2" t="inlineStr"/>
+      <c r="X183" s="2" t="inlineStr"/>
+      <c r="Y183" s="2" t="inlineStr"/>
+      <c r="Z183" s="2" t="inlineStr"/>
+      <c r="AA183" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Serbia.xlsx
+++ b/BWI/bestwine_output/bestwine_Serbia.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA183"/>
+  <dimension ref="A1:AA185"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -20267,6 +20267,204 @@
       <c r="Z183" s="2" t="inlineStr"/>
       <c r="AA183" s="2" t="inlineStr"/>
     </row>
+    <row r="184">
+      <c r="A184" s="2" t="inlineStr">
+        <is>
+          <t>Idea D.o.o.</t>
+        </is>
+      </c>
+      <c r="B184" s="2" t="inlineStr">
+        <is>
+          <t>Idea D.o.o.</t>
+        </is>
+      </c>
+      <c r="C184" s="2" t="inlineStr">
+        <is>
+          <t>110412</t>
+        </is>
+      </c>
+      <c r="D184" s="2" t="inlineStr">
+        <is>
+          <t>Serbia</t>
+        </is>
+      </c>
+      <c r="E184" s="2" t="inlineStr">
+        <is>
+          <t>Belgrade</t>
+        </is>
+      </c>
+      <c r="F184" s="2" t="inlineStr">
+        <is>
+          <t>Belgrade</t>
+        </is>
+      </c>
+      <c r="G184" s="2" t="inlineStr">
+        <is>
+          <t>Autoput Za Zagreb 11a.</t>
+        </is>
+      </c>
+      <c r="H184" s="2" t="inlineStr">
+        <is>
+          <t>11283</t>
+        </is>
+      </c>
+      <c r="I184" s="2" t="inlineStr">
+        <is>
+          <t>https://online.idea.rs, https://www.idea.rs</t>
+        </is>
+      </c>
+      <c r="J184" s="2" t="inlineStr"/>
+      <c r="K184" s="2" t="inlineStr"/>
+      <c r="L184" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M184" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N184" s="2" t="inlineStr">
+        <is>
+          <t>online@idea.rs</t>
+        </is>
+      </c>
+      <c r="O184" s="2" t="inlineStr">
+        <is>
+          <t>+381 800 101202</t>
+        </is>
+      </c>
+      <c r="P184" s="2" t="inlineStr">
+        <is>
+          <t>1992</t>
+        </is>
+      </c>
+      <c r="Q184" s="2" t="inlineStr">
+        <is>
+          <t>06423566</t>
+        </is>
+      </c>
+      <c r="R184" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/idea-d.o.o./</t>
+        </is>
+      </c>
+      <c r="S184" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/IDEASrbija/</t>
+        </is>
+      </c>
+      <c r="T184" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/ideasrbija</t>
+        </is>
+      </c>
+      <c r="U184" s="2" t="inlineStr"/>
+      <c r="V184" s="2" t="inlineStr"/>
+      <c r="W184" s="2" t="inlineStr"/>
+      <c r="X184" s="2" t="inlineStr"/>
+      <c r="Y184" s="2" t="inlineStr"/>
+      <c r="Z184" s="2" t="inlineStr"/>
+      <c r="AA184" s="2" t="inlineStr"/>
+    </row>
+    <row r="185">
+      <c r="A185" s="2" t="inlineStr">
+        <is>
+          <t>Dan Company Doo</t>
+        </is>
+      </c>
+      <c r="B185" s="2" t="inlineStr">
+        <is>
+          <t>Dan Company Doo</t>
+        </is>
+      </c>
+      <c r="C185" s="2" t="inlineStr">
+        <is>
+          <t>32642</t>
+        </is>
+      </c>
+      <c r="D185" s="2" t="inlineStr">
+        <is>
+          <t>Serbia</t>
+        </is>
+      </c>
+      <c r="E185" s="2" t="inlineStr">
+        <is>
+          <t>Beograd</t>
+        </is>
+      </c>
+      <c r="F185" s="2" t="inlineStr">
+        <is>
+          <t>Grad Beograd</t>
+        </is>
+      </c>
+      <c r="G185" s="2" t="inlineStr">
+        <is>
+          <t>41 Lomina</t>
+        </is>
+      </c>
+      <c r="H185" s="2" t="inlineStr">
+        <is>
+          <t>11000</t>
+        </is>
+      </c>
+      <c r="I185" s="2" t="inlineStr">
+        <is>
+          <t>https://dan-company.com</t>
+        </is>
+      </c>
+      <c r="J185" s="2" t="inlineStr"/>
+      <c r="K185" s="2" t="inlineStr"/>
+      <c r="L185" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M185" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N185" s="2" t="inlineStr">
+        <is>
+          <t>office@dan-company.com</t>
+        </is>
+      </c>
+      <c r="O185" s="2" t="inlineStr">
+        <is>
+          <t>+381 11 2644148</t>
+        </is>
+      </c>
+      <c r="P185" s="2" t="inlineStr">
+        <is>
+          <t>1992</t>
+        </is>
+      </c>
+      <c r="Q185" s="2" t="inlineStr">
+        <is>
+          <t>06205976</t>
+        </is>
+      </c>
+      <c r="R185" s="2" t="inlineStr"/>
+      <c r="S185" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/vinotekachianti/</t>
+        </is>
+      </c>
+      <c r="T185" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/vinoteka_chianti/</t>
+        </is>
+      </c>
+      <c r="U185" s="2" t="inlineStr"/>
+      <c r="V185" s="2" t="inlineStr"/>
+      <c r="W185" s="2" t="inlineStr"/>
+      <c r="X185" s="2" t="inlineStr"/>
+      <c r="Y185" s="2" t="inlineStr"/>
+      <c r="Z185" s="2" t="inlineStr"/>
+      <c r="AA185" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Serbia.xlsx
+++ b/BWI/bestwine_output/bestwine_Serbia.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA185"/>
+  <dimension ref="A1:AA187"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -20465,6 +20465,204 @@
       <c r="Z185" s="2" t="inlineStr"/>
       <c r="AA185" s="2" t="inlineStr"/>
     </row>
+    <row r="186">
+      <c r="A186" s="2" t="inlineStr">
+        <is>
+          <t>Idea D.o.o.</t>
+        </is>
+      </c>
+      <c r="B186" s="2" t="inlineStr">
+        <is>
+          <t>Idea D.o.o.</t>
+        </is>
+      </c>
+      <c r="C186" s="2" t="inlineStr">
+        <is>
+          <t>110412</t>
+        </is>
+      </c>
+      <c r="D186" s="2" t="inlineStr">
+        <is>
+          <t>Serbia</t>
+        </is>
+      </c>
+      <c r="E186" s="2" t="inlineStr">
+        <is>
+          <t>Belgrade</t>
+        </is>
+      </c>
+      <c r="F186" s="2" t="inlineStr">
+        <is>
+          <t>Belgrade</t>
+        </is>
+      </c>
+      <c r="G186" s="2" t="inlineStr">
+        <is>
+          <t>Autoput Za Zagreb 11a.</t>
+        </is>
+      </c>
+      <c r="H186" s="2" t="inlineStr">
+        <is>
+          <t>11283</t>
+        </is>
+      </c>
+      <c r="I186" s="2" t="inlineStr">
+        <is>
+          <t>https://online.idea.rs, https://www.idea.rs</t>
+        </is>
+      </c>
+      <c r="J186" s="2" t="inlineStr"/>
+      <c r="K186" s="2" t="inlineStr"/>
+      <c r="L186" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M186" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N186" s="2" t="inlineStr">
+        <is>
+          <t>online@idea.rs</t>
+        </is>
+      </c>
+      <c r="O186" s="2" t="inlineStr">
+        <is>
+          <t>+381 800 101202</t>
+        </is>
+      </c>
+      <c r="P186" s="2" t="inlineStr">
+        <is>
+          <t>1992</t>
+        </is>
+      </c>
+      <c r="Q186" s="2" t="inlineStr">
+        <is>
+          <t>06423566</t>
+        </is>
+      </c>
+      <c r="R186" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/idea-d.o.o./</t>
+        </is>
+      </c>
+      <c r="S186" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/IDEASrbija/</t>
+        </is>
+      </c>
+      <c r="T186" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/ideasrbija</t>
+        </is>
+      </c>
+      <c r="U186" s="2" t="inlineStr"/>
+      <c r="V186" s="2" t="inlineStr"/>
+      <c r="W186" s="2" t="inlineStr"/>
+      <c r="X186" s="2" t="inlineStr"/>
+      <c r="Y186" s="2" t="inlineStr"/>
+      <c r="Z186" s="2" t="inlineStr"/>
+      <c r="AA186" s="2" t="inlineStr"/>
+    </row>
+    <row r="187">
+      <c r="A187" s="2" t="inlineStr">
+        <is>
+          <t>Dan Company Doo</t>
+        </is>
+      </c>
+      <c r="B187" s="2" t="inlineStr">
+        <is>
+          <t>Dan Company Doo</t>
+        </is>
+      </c>
+      <c r="C187" s="2" t="inlineStr">
+        <is>
+          <t>32642</t>
+        </is>
+      </c>
+      <c r="D187" s="2" t="inlineStr">
+        <is>
+          <t>Serbia</t>
+        </is>
+      </c>
+      <c r="E187" s="2" t="inlineStr">
+        <is>
+          <t>Beograd</t>
+        </is>
+      </c>
+      <c r="F187" s="2" t="inlineStr">
+        <is>
+          <t>Grad Beograd</t>
+        </is>
+      </c>
+      <c r="G187" s="2" t="inlineStr">
+        <is>
+          <t>41 Lomina</t>
+        </is>
+      </c>
+      <c r="H187" s="2" t="inlineStr">
+        <is>
+          <t>11000</t>
+        </is>
+      </c>
+      <c r="I187" s="2" t="inlineStr">
+        <is>
+          <t>https://dan-company.com</t>
+        </is>
+      </c>
+      <c r="J187" s="2" t="inlineStr"/>
+      <c r="K187" s="2" t="inlineStr"/>
+      <c r="L187" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M187" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N187" s="2" t="inlineStr">
+        <is>
+          <t>office@dan-company.com</t>
+        </is>
+      </c>
+      <c r="O187" s="2" t="inlineStr">
+        <is>
+          <t>+381 11 2644148</t>
+        </is>
+      </c>
+      <c r="P187" s="2" t="inlineStr">
+        <is>
+          <t>1992</t>
+        </is>
+      </c>
+      <c r="Q187" s="2" t="inlineStr">
+        <is>
+          <t>06205976</t>
+        </is>
+      </c>
+      <c r="R187" s="2" t="inlineStr"/>
+      <c r="S187" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/vinotekachianti/</t>
+        </is>
+      </c>
+      <c r="T187" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/vinoteka_chianti/</t>
+        </is>
+      </c>
+      <c r="U187" s="2" t="inlineStr"/>
+      <c r="V187" s="2" t="inlineStr"/>
+      <c r="W187" s="2" t="inlineStr"/>
+      <c r="X187" s="2" t="inlineStr"/>
+      <c r="Y187" s="2" t="inlineStr"/>
+      <c r="Z187" s="2" t="inlineStr"/>
+      <c r="AA187" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Serbia.xlsx
+++ b/BWI/bestwine_output/bestwine_Serbia.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA187"/>
+  <dimension ref="A1:AA189"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -20663,6 +20663,204 @@
       <c r="Z187" s="2" t="inlineStr"/>
       <c r="AA187" s="2" t="inlineStr"/>
     </row>
+    <row r="188">
+      <c r="A188" s="2" t="inlineStr">
+        <is>
+          <t>Idea D.o.o.</t>
+        </is>
+      </c>
+      <c r="B188" s="2" t="inlineStr">
+        <is>
+          <t>Idea D.o.o.</t>
+        </is>
+      </c>
+      <c r="C188" s="2" t="inlineStr">
+        <is>
+          <t>110412</t>
+        </is>
+      </c>
+      <c r="D188" s="2" t="inlineStr">
+        <is>
+          <t>Serbia</t>
+        </is>
+      </c>
+      <c r="E188" s="2" t="inlineStr">
+        <is>
+          <t>Belgrade</t>
+        </is>
+      </c>
+      <c r="F188" s="2" t="inlineStr">
+        <is>
+          <t>Belgrade</t>
+        </is>
+      </c>
+      <c r="G188" s="2" t="inlineStr">
+        <is>
+          <t>Autoput Za Zagreb 11a.</t>
+        </is>
+      </c>
+      <c r="H188" s="2" t="inlineStr">
+        <is>
+          <t>11283</t>
+        </is>
+      </c>
+      <c r="I188" s="2" t="inlineStr">
+        <is>
+          <t>https://online.idea.rs, https://www.idea.rs</t>
+        </is>
+      </c>
+      <c r="J188" s="2" t="inlineStr"/>
+      <c r="K188" s="2" t="inlineStr"/>
+      <c r="L188" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M188" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N188" s="2" t="inlineStr">
+        <is>
+          <t>online@idea.rs</t>
+        </is>
+      </c>
+      <c r="O188" s="2" t="inlineStr">
+        <is>
+          <t>+381 800 101202</t>
+        </is>
+      </c>
+      <c r="P188" s="2" t="inlineStr">
+        <is>
+          <t>1992</t>
+        </is>
+      </c>
+      <c r="Q188" s="2" t="inlineStr">
+        <is>
+          <t>06423566</t>
+        </is>
+      </c>
+      <c r="R188" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/idea-d.o.o./</t>
+        </is>
+      </c>
+      <c r="S188" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/IDEASrbija/</t>
+        </is>
+      </c>
+      <c r="T188" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/ideasrbija</t>
+        </is>
+      </c>
+      <c r="U188" s="2" t="inlineStr"/>
+      <c r="V188" s="2" t="inlineStr"/>
+      <c r="W188" s="2" t="inlineStr"/>
+      <c r="X188" s="2" t="inlineStr"/>
+      <c r="Y188" s="2" t="inlineStr"/>
+      <c r="Z188" s="2" t="inlineStr"/>
+      <c r="AA188" s="2" t="inlineStr"/>
+    </row>
+    <row r="189">
+      <c r="A189" s="2" t="inlineStr">
+        <is>
+          <t>Dan Company Doo</t>
+        </is>
+      </c>
+      <c r="B189" s="2" t="inlineStr">
+        <is>
+          <t>Dan Company Doo</t>
+        </is>
+      </c>
+      <c r="C189" s="2" t="inlineStr">
+        <is>
+          <t>32642</t>
+        </is>
+      </c>
+      <c r="D189" s="2" t="inlineStr">
+        <is>
+          <t>Serbia</t>
+        </is>
+      </c>
+      <c r="E189" s="2" t="inlineStr">
+        <is>
+          <t>Beograd</t>
+        </is>
+      </c>
+      <c r="F189" s="2" t="inlineStr">
+        <is>
+          <t>Grad Beograd</t>
+        </is>
+      </c>
+      <c r="G189" s="2" t="inlineStr">
+        <is>
+          <t>41 Lomina</t>
+        </is>
+      </c>
+      <c r="H189" s="2" t="inlineStr">
+        <is>
+          <t>11000</t>
+        </is>
+      </c>
+      <c r="I189" s="2" t="inlineStr">
+        <is>
+          <t>https://dan-company.com</t>
+        </is>
+      </c>
+      <c r="J189" s="2" t="inlineStr"/>
+      <c r="K189" s="2" t="inlineStr"/>
+      <c r="L189" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M189" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N189" s="2" t="inlineStr">
+        <is>
+          <t>office@dan-company.com</t>
+        </is>
+      </c>
+      <c r="O189" s="2" t="inlineStr">
+        <is>
+          <t>+381 11 2644148</t>
+        </is>
+      </c>
+      <c r="P189" s="2" t="inlineStr">
+        <is>
+          <t>1992</t>
+        </is>
+      </c>
+      <c r="Q189" s="2" t="inlineStr">
+        <is>
+          <t>06205976</t>
+        </is>
+      </c>
+      <c r="R189" s="2" t="inlineStr"/>
+      <c r="S189" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/vinotekachianti/</t>
+        </is>
+      </c>
+      <c r="T189" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/vinoteka_chianti/</t>
+        </is>
+      </c>
+      <c r="U189" s="2" t="inlineStr"/>
+      <c r="V189" s="2" t="inlineStr"/>
+      <c r="W189" s="2" t="inlineStr"/>
+      <c r="X189" s="2" t="inlineStr"/>
+      <c r="Y189" s="2" t="inlineStr"/>
+      <c r="Z189" s="2" t="inlineStr"/>
+      <c r="AA189" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Serbia.xlsx
+++ b/BWI/bestwine_output/bestwine_Serbia.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA189"/>
+  <dimension ref="A1:AA192"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -20861,6 +20861,345 @@
       <c r="Z189" s="2" t="inlineStr"/>
       <c r="AA189" s="2" t="inlineStr"/>
     </row>
+    <row r="190">
+      <c r="A190" s="2" t="inlineStr">
+        <is>
+          <t>Metro Cash &amp; Carry D.o.o.</t>
+        </is>
+      </c>
+      <c r="B190" s="2" t="inlineStr">
+        <is>
+          <t>Metro Cash &amp; Carry D.o.o.</t>
+        </is>
+      </c>
+      <c r="C190" s="2" t="inlineStr">
+        <is>
+          <t>108569</t>
+        </is>
+      </c>
+      <c r="D190" s="2" t="inlineStr">
+        <is>
+          <t>Serbia</t>
+        </is>
+      </c>
+      <c r="E190" s="2" t="inlineStr">
+        <is>
+          <t>Beograd</t>
+        </is>
+      </c>
+      <c r="F190" s="2" t="inlineStr">
+        <is>
+          <t>Grad Beograd</t>
+        </is>
+      </c>
+      <c r="G190" s="2" t="inlineStr">
+        <is>
+          <t>120 Autoput Za Novi Sad</t>
+        </is>
+      </c>
+      <c r="H190" s="2" t="inlineStr">
+        <is>
+          <t>11080</t>
+        </is>
+      </c>
+      <c r="I190" s="2" t="inlineStr">
+        <is>
+          <t>https://www.metro.rs</t>
+        </is>
+      </c>
+      <c r="J190" s="2" t="inlineStr"/>
+      <c r="K190" s="2" t="inlineStr"/>
+      <c r="L190" s="2" t="inlineStr">
+        <is>
+          <t>1179</t>
+        </is>
+      </c>
+      <c r="M190" s="2" t="inlineStr"/>
+      <c r="N190" s="2" t="inlineStr">
+        <is>
+          <t>info@metro.rs</t>
+        </is>
+      </c>
+      <c r="O190" s="2" t="inlineStr">
+        <is>
+          <t>+381 800 222022</t>
+        </is>
+      </c>
+      <c r="P190" s="2" t="inlineStr">
+        <is>
+          <t>2003</t>
+        </is>
+      </c>
+      <c r="Q190" s="2" t="inlineStr">
+        <is>
+          <t>17482700</t>
+        </is>
+      </c>
+      <c r="R190" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/metro-cash&amp;carry-doo-serbia/</t>
+        </is>
+      </c>
+      <c r="S190" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/MetroSrb</t>
+        </is>
+      </c>
+      <c r="T190" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/metro_srbija/</t>
+        </is>
+      </c>
+      <c r="U190" s="2" t="inlineStr"/>
+      <c r="V190" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/channel/UC1i_5rMZgL2Mb-Xjg0g3S5Q</t>
+        </is>
+      </c>
+      <c r="W190" s="2" t="inlineStr">
+        <is>
+          <t>Nemanja Bogavac</t>
+        </is>
+      </c>
+      <c r="X190" s="2" t="inlineStr">
+        <is>
+          <t>Head of Fresh/ Ultra Fresh and Beverage Departments</t>
+        </is>
+      </c>
+      <c r="Y190" s="2" t="inlineStr"/>
+      <c r="Z190" s="2" t="inlineStr"/>
+      <c r="AA190" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/nemanja-bogavac-512b57113/</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="2" t="inlineStr">
+        <is>
+          <t>Metro Cash &amp; Carry D.o.o.</t>
+        </is>
+      </c>
+      <c r="B191" s="2" t="inlineStr">
+        <is>
+          <t>Metro Cash &amp; Carry D.o.o.</t>
+        </is>
+      </c>
+      <c r="C191" s="2" t="inlineStr">
+        <is>
+          <t>108569</t>
+        </is>
+      </c>
+      <c r="D191" s="2" t="inlineStr">
+        <is>
+          <t>Serbia</t>
+        </is>
+      </c>
+      <c r="E191" s="2" t="inlineStr">
+        <is>
+          <t>Beograd</t>
+        </is>
+      </c>
+      <c r="F191" s="2" t="inlineStr">
+        <is>
+          <t>Grad Beograd</t>
+        </is>
+      </c>
+      <c r="G191" s="2" t="inlineStr">
+        <is>
+          <t>120 Autoput Za Novi Sad</t>
+        </is>
+      </c>
+      <c r="H191" s="2" t="inlineStr">
+        <is>
+          <t>11080</t>
+        </is>
+      </c>
+      <c r="I191" s="2" t="inlineStr">
+        <is>
+          <t>https://www.metro.rs</t>
+        </is>
+      </c>
+      <c r="J191" s="2" t="inlineStr"/>
+      <c r="K191" s="2" t="inlineStr"/>
+      <c r="L191" s="2" t="inlineStr">
+        <is>
+          <t>1179</t>
+        </is>
+      </c>
+      <c r="M191" s="2" t="inlineStr"/>
+      <c r="N191" s="2" t="inlineStr">
+        <is>
+          <t>info@metro.rs</t>
+        </is>
+      </c>
+      <c r="O191" s="2" t="inlineStr">
+        <is>
+          <t>+381 800 222022</t>
+        </is>
+      </c>
+      <c r="P191" s="2" t="inlineStr">
+        <is>
+          <t>2003</t>
+        </is>
+      </c>
+      <c r="Q191" s="2" t="inlineStr">
+        <is>
+          <t>17482700</t>
+        </is>
+      </c>
+      <c r="R191" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/metro-cash&amp;carry-doo-serbia/</t>
+        </is>
+      </c>
+      <c r="S191" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/MetroSrb</t>
+        </is>
+      </c>
+      <c r="T191" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/metro_srbija/</t>
+        </is>
+      </c>
+      <c r="U191" s="2" t="inlineStr"/>
+      <c r="V191" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/channel/UC1i_5rMZgL2Mb-Xjg0g3S5Q</t>
+        </is>
+      </c>
+      <c r="W191" s="2" t="inlineStr">
+        <is>
+          <t>Lazar Ćiraković</t>
+        </is>
+      </c>
+      <c r="X191" s="2" t="inlineStr">
+        <is>
+          <t>Logistics Operations Manager</t>
+        </is>
+      </c>
+      <c r="Y191" s="2" t="inlineStr"/>
+      <c r="Z191" s="2" t="inlineStr"/>
+      <c r="AA191" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/cirakoviclazar/</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="2" t="inlineStr">
+        <is>
+          <t>Metro Cash &amp; Carry D.o.o.</t>
+        </is>
+      </c>
+      <c r="B192" s="2" t="inlineStr">
+        <is>
+          <t>Metro Cash &amp; Carry D.o.o.</t>
+        </is>
+      </c>
+      <c r="C192" s="2" t="inlineStr">
+        <is>
+          <t>108569</t>
+        </is>
+      </c>
+      <c r="D192" s="2" t="inlineStr">
+        <is>
+          <t>Serbia</t>
+        </is>
+      </c>
+      <c r="E192" s="2" t="inlineStr">
+        <is>
+          <t>Beograd</t>
+        </is>
+      </c>
+      <c r="F192" s="2" t="inlineStr">
+        <is>
+          <t>Grad Beograd</t>
+        </is>
+      </c>
+      <c r="G192" s="2" t="inlineStr">
+        <is>
+          <t>120 Autoput Za Novi Sad</t>
+        </is>
+      </c>
+      <c r="H192" s="2" t="inlineStr">
+        <is>
+          <t>11080</t>
+        </is>
+      </c>
+      <c r="I192" s="2" t="inlineStr">
+        <is>
+          <t>https://www.metro.rs</t>
+        </is>
+      </c>
+      <c r="J192" s="2" t="inlineStr"/>
+      <c r="K192" s="2" t="inlineStr"/>
+      <c r="L192" s="2" t="inlineStr">
+        <is>
+          <t>1179</t>
+        </is>
+      </c>
+      <c r="M192" s="2" t="inlineStr"/>
+      <c r="N192" s="2" t="inlineStr">
+        <is>
+          <t>info@metro.rs</t>
+        </is>
+      </c>
+      <c r="O192" s="2" t="inlineStr">
+        <is>
+          <t>+381 800 222022</t>
+        </is>
+      </c>
+      <c r="P192" s="2" t="inlineStr">
+        <is>
+          <t>2003</t>
+        </is>
+      </c>
+      <c r="Q192" s="2" t="inlineStr">
+        <is>
+          <t>17482700</t>
+        </is>
+      </c>
+      <c r="R192" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/metro-cash&amp;carry-doo-serbia/</t>
+        </is>
+      </c>
+      <c r="S192" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/MetroSrb</t>
+        </is>
+      </c>
+      <c r="T192" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/metro_srbija/</t>
+        </is>
+      </c>
+      <c r="U192" s="2" t="inlineStr"/>
+      <c r="V192" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/channel/UC1i_5rMZgL2Mb-Xjg0g3S5Q</t>
+        </is>
+      </c>
+      <c r="W192" s="2" t="inlineStr">
+        <is>
+          <t>Jasmina Manojlović</t>
+        </is>
+      </c>
+      <c r="X192" s="2" t="inlineStr">
+        <is>
+          <t>Procurement Specialist</t>
+        </is>
+      </c>
+      <c r="Y192" s="2" t="inlineStr"/>
+      <c r="Z192" s="2" t="inlineStr"/>
+      <c r="AA192" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/jasmina-manojlovi%C4%87-647361286/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Serbia.xlsx
+++ b/BWI/bestwine_output/bestwine_Serbia.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA192"/>
+  <dimension ref="A1:AA196"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -21200,6 +21200,410 @@
         </is>
       </c>
     </row>
+    <row r="193">
+      <c r="A193" s="2" t="inlineStr">
+        <is>
+          <t>Ktk Komerc D.o.o.</t>
+        </is>
+      </c>
+      <c r="B193" s="2" t="inlineStr">
+        <is>
+          <t>Ktk Komerc D.o.o.</t>
+        </is>
+      </c>
+      <c r="C193" s="2" t="inlineStr">
+        <is>
+          <t>146429</t>
+        </is>
+      </c>
+      <c r="D193" s="2" t="inlineStr">
+        <is>
+          <t>Serbia</t>
+        </is>
+      </c>
+      <c r="E193" s="2" t="inlineStr">
+        <is>
+          <t>Kruševac</t>
+        </is>
+      </c>
+      <c r="F193" s="2" t="inlineStr">
+        <is>
+          <t>Rasinski Okrug</t>
+        </is>
+      </c>
+      <c r="G193" s="2" t="inlineStr">
+        <is>
+          <t>81 Balkanska</t>
+        </is>
+      </c>
+      <c r="H193" s="2" t="inlineStr"/>
+      <c r="I193" s="2" t="inlineStr">
+        <is>
+          <t>https://ktkmarketi.com</t>
+        </is>
+      </c>
+      <c r="J193" s="2" t="inlineStr"/>
+      <c r="K193" s="2" t="inlineStr"/>
+      <c r="L193" s="2" t="inlineStr">
+        <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="M193" s="2" t="inlineStr"/>
+      <c r="N193" s="2" t="inlineStr">
+        <is>
+          <t>marketiktk@gmail.com</t>
+        </is>
+      </c>
+      <c r="O193" s="2" t="inlineStr">
+        <is>
+          <t>+381 37 448620</t>
+        </is>
+      </c>
+      <c r="P193" s="2" t="inlineStr">
+        <is>
+          <t>1998</t>
+        </is>
+      </c>
+      <c r="Q193" s="2" t="inlineStr">
+        <is>
+          <t>07852398</t>
+        </is>
+      </c>
+      <c r="R193" s="2" t="inlineStr"/>
+      <c r="S193" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/ktkmarketi/</t>
+        </is>
+      </c>
+      <c r="T193" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/ktk.marketi</t>
+        </is>
+      </c>
+      <c r="U193" s="2" t="inlineStr"/>
+      <c r="V193" s="2" t="inlineStr"/>
+      <c r="W193" s="2" t="inlineStr">
+        <is>
+          <t>Neša Ktk</t>
+        </is>
+      </c>
+      <c r="X193" s="2" t="inlineStr">
+        <is>
+          <t>Ceo</t>
+        </is>
+      </c>
+      <c r="Y193" s="2" t="inlineStr"/>
+      <c r="Z193" s="2" t="inlineStr"/>
+      <c r="AA193" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/ne%C5%A1a-ktk-1757b027a/</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="2" t="inlineStr">
+        <is>
+          <t>Knjaz Milos-natura Doo Beograd</t>
+        </is>
+      </c>
+      <c r="B194" s="2" t="inlineStr">
+        <is>
+          <t>Knjaz Milos-natura Doo Beograd</t>
+        </is>
+      </c>
+      <c r="C194" s="2" t="inlineStr">
+        <is>
+          <t>122245</t>
+        </is>
+      </c>
+      <c r="D194" s="2" t="inlineStr">
+        <is>
+          <t>Serbia</t>
+        </is>
+      </c>
+      <c r="E194" s="2" t="inlineStr">
+        <is>
+          <t>Beograd</t>
+        </is>
+      </c>
+      <c r="F194" s="2" t="inlineStr">
+        <is>
+          <t>Grad Beograd</t>
+        </is>
+      </c>
+      <c r="G194" s="2" t="inlineStr">
+        <is>
+          <t>41 Bulevar Peka Dapčevića</t>
+        </is>
+      </c>
+      <c r="H194" s="2" t="inlineStr">
+        <is>
+          <t>11152</t>
+        </is>
+      </c>
+      <c r="I194" s="2" t="inlineStr">
+        <is>
+          <t>https://www.knjaznatura.co.rs</t>
+        </is>
+      </c>
+      <c r="J194" s="2" t="inlineStr"/>
+      <c r="K194" s="2" t="inlineStr"/>
+      <c r="L194" s="2" t="inlineStr">
+        <is>
+          <t>140</t>
+        </is>
+      </c>
+      <c r="M194" s="2" t="inlineStr"/>
+      <c r="N194" s="2" t="inlineStr">
+        <is>
+          <t>office@knjaznatura.co.rs</t>
+        </is>
+      </c>
+      <c r="O194" s="2" t="inlineStr">
+        <is>
+          <t>+381 800 000008</t>
+        </is>
+      </c>
+      <c r="P194" s="2" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="Q194" s="2" t="inlineStr">
+        <is>
+          <t>20350229</t>
+        </is>
+      </c>
+      <c r="R194" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/knjazmilosnatura/</t>
+        </is>
+      </c>
+      <c r="S194" s="2" t="inlineStr"/>
+      <c r="T194" s="2" t="inlineStr"/>
+      <c r="U194" s="2" t="inlineStr"/>
+      <c r="V194" s="2" t="inlineStr"/>
+      <c r="W194" s="2" t="inlineStr">
+        <is>
+          <t>Dušan Mančić</t>
+        </is>
+      </c>
+      <c r="X194" s="2" t="inlineStr">
+        <is>
+          <t>Head Of Sales</t>
+        </is>
+      </c>
+      <c r="Y194" s="2" t="inlineStr"/>
+      <c r="Z194" s="2" t="inlineStr"/>
+      <c r="AA194" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/du%C5%A1an-man%C4%8Di%C4%87-62822a46/</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="2" t="inlineStr">
+        <is>
+          <t>Knjaz Milos-natura Doo Beograd</t>
+        </is>
+      </c>
+      <c r="B195" s="2" t="inlineStr">
+        <is>
+          <t>Knjaz Milos-natura Doo Beograd</t>
+        </is>
+      </c>
+      <c r="C195" s="2" t="inlineStr">
+        <is>
+          <t>122245</t>
+        </is>
+      </c>
+      <c r="D195" s="2" t="inlineStr">
+        <is>
+          <t>Serbia</t>
+        </is>
+      </c>
+      <c r="E195" s="2" t="inlineStr">
+        <is>
+          <t>Beograd</t>
+        </is>
+      </c>
+      <c r="F195" s="2" t="inlineStr">
+        <is>
+          <t>Grad Beograd</t>
+        </is>
+      </c>
+      <c r="G195" s="2" t="inlineStr">
+        <is>
+          <t>41 Bulevar Peka Dapčevića</t>
+        </is>
+      </c>
+      <c r="H195" s="2" t="inlineStr">
+        <is>
+          <t>11152</t>
+        </is>
+      </c>
+      <c r="I195" s="2" t="inlineStr">
+        <is>
+          <t>https://www.knjaznatura.co.rs</t>
+        </is>
+      </c>
+      <c r="J195" s="2" t="inlineStr"/>
+      <c r="K195" s="2" t="inlineStr"/>
+      <c r="L195" s="2" t="inlineStr">
+        <is>
+          <t>140</t>
+        </is>
+      </c>
+      <c r="M195" s="2" t="inlineStr"/>
+      <c r="N195" s="2" t="inlineStr">
+        <is>
+          <t>office@knjaznatura.co.rs</t>
+        </is>
+      </c>
+      <c r="O195" s="2" t="inlineStr">
+        <is>
+          <t>+381 800 000008</t>
+        </is>
+      </c>
+      <c r="P195" s="2" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="Q195" s="2" t="inlineStr">
+        <is>
+          <t>20350229</t>
+        </is>
+      </c>
+      <c r="R195" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/knjazmilosnatura/</t>
+        </is>
+      </c>
+      <c r="S195" s="2" t="inlineStr"/>
+      <c r="T195" s="2" t="inlineStr"/>
+      <c r="U195" s="2" t="inlineStr"/>
+      <c r="V195" s="2" t="inlineStr"/>
+      <c r="W195" s="2" t="inlineStr">
+        <is>
+          <t>Srdjan Martic</t>
+        </is>
+      </c>
+      <c r="X195" s="2" t="inlineStr">
+        <is>
+          <t>Regional Sales Representative</t>
+        </is>
+      </c>
+      <c r="Y195" s="2" t="inlineStr"/>
+      <c r="Z195" s="2" t="inlineStr"/>
+      <c r="AA195" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/srdjan-martic-092122254/</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="2" t="inlineStr">
+        <is>
+          <t>Knjaz Milos-natura Doo Beograd</t>
+        </is>
+      </c>
+      <c r="B196" s="2" t="inlineStr">
+        <is>
+          <t>Knjaz Milos-natura Doo Beograd</t>
+        </is>
+      </c>
+      <c r="C196" s="2" t="inlineStr">
+        <is>
+          <t>122245</t>
+        </is>
+      </c>
+      <c r="D196" s="2" t="inlineStr">
+        <is>
+          <t>Serbia</t>
+        </is>
+      </c>
+      <c r="E196" s="2" t="inlineStr">
+        <is>
+          <t>Beograd</t>
+        </is>
+      </c>
+      <c r="F196" s="2" t="inlineStr">
+        <is>
+          <t>Grad Beograd</t>
+        </is>
+      </c>
+      <c r="G196" s="2" t="inlineStr">
+        <is>
+          <t>41 Bulevar Peka Dapčevića</t>
+        </is>
+      </c>
+      <c r="H196" s="2" t="inlineStr">
+        <is>
+          <t>11152</t>
+        </is>
+      </c>
+      <c r="I196" s="2" t="inlineStr">
+        <is>
+          <t>https://www.knjaznatura.co.rs</t>
+        </is>
+      </c>
+      <c r="J196" s="2" t="inlineStr"/>
+      <c r="K196" s="2" t="inlineStr"/>
+      <c r="L196" s="2" t="inlineStr">
+        <is>
+          <t>140</t>
+        </is>
+      </c>
+      <c r="M196" s="2" t="inlineStr"/>
+      <c r="N196" s="2" t="inlineStr">
+        <is>
+          <t>office@knjaznatura.co.rs</t>
+        </is>
+      </c>
+      <c r="O196" s="2" t="inlineStr">
+        <is>
+          <t>+381 800 000008</t>
+        </is>
+      </c>
+      <c r="P196" s="2" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="Q196" s="2" t="inlineStr">
+        <is>
+          <t>20350229</t>
+        </is>
+      </c>
+      <c r="R196" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/knjazmilosnatura/</t>
+        </is>
+      </c>
+      <c r="S196" s="2" t="inlineStr"/>
+      <c r="T196" s="2" t="inlineStr"/>
+      <c r="U196" s="2" t="inlineStr"/>
+      <c r="V196" s="2" t="inlineStr"/>
+      <c r="W196" s="2" t="inlineStr">
+        <is>
+          <t>Dejan Pantic</t>
+        </is>
+      </c>
+      <c r="X196" s="2" t="inlineStr">
+        <is>
+          <t>Logistics Manager</t>
+        </is>
+      </c>
+      <c r="Y196" s="2" t="inlineStr"/>
+      <c r="Z196" s="2" t="inlineStr"/>
+      <c r="AA196" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/dejan-pantic-b1750ab9/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Serbia.xlsx
+++ b/BWI/bestwine_output/bestwine_Serbia.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA196"/>
+  <dimension ref="A1:AA200"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -21604,6 +21604,410 @@
         </is>
       </c>
     </row>
+    <row r="197">
+      <c r="A197" s="2" t="inlineStr">
+        <is>
+          <t>Ktk Komerc D.o.o.</t>
+        </is>
+      </c>
+      <c r="B197" s="2" t="inlineStr">
+        <is>
+          <t>Ktk Komerc D.o.o.</t>
+        </is>
+      </c>
+      <c r="C197" s="2" t="inlineStr">
+        <is>
+          <t>146429</t>
+        </is>
+      </c>
+      <c r="D197" s="2" t="inlineStr">
+        <is>
+          <t>Serbia</t>
+        </is>
+      </c>
+      <c r="E197" s="2" t="inlineStr">
+        <is>
+          <t>Kruševac</t>
+        </is>
+      </c>
+      <c r="F197" s="2" t="inlineStr">
+        <is>
+          <t>Rasinski Okrug</t>
+        </is>
+      </c>
+      <c r="G197" s="2" t="inlineStr">
+        <is>
+          <t>81 Balkanska</t>
+        </is>
+      </c>
+      <c r="H197" s="2" t="inlineStr"/>
+      <c r="I197" s="2" t="inlineStr">
+        <is>
+          <t>https://ktkmarketi.com</t>
+        </is>
+      </c>
+      <c r="J197" s="2" t="inlineStr"/>
+      <c r="K197" s="2" t="inlineStr"/>
+      <c r="L197" s="2" t="inlineStr">
+        <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="M197" s="2" t="inlineStr"/>
+      <c r="N197" s="2" t="inlineStr">
+        <is>
+          <t>marketiktk@gmail.com</t>
+        </is>
+      </c>
+      <c r="O197" s="2" t="inlineStr">
+        <is>
+          <t>+381 37 448620</t>
+        </is>
+      </c>
+      <c r="P197" s="2" t="inlineStr">
+        <is>
+          <t>1998</t>
+        </is>
+      </c>
+      <c r="Q197" s="2" t="inlineStr">
+        <is>
+          <t>07852398</t>
+        </is>
+      </c>
+      <c r="R197" s="2" t="inlineStr"/>
+      <c r="S197" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/ktkmarketi/</t>
+        </is>
+      </c>
+      <c r="T197" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/ktk.marketi</t>
+        </is>
+      </c>
+      <c r="U197" s="2" t="inlineStr"/>
+      <c r="V197" s="2" t="inlineStr"/>
+      <c r="W197" s="2" t="inlineStr">
+        <is>
+          <t>Neša Ktk</t>
+        </is>
+      </c>
+      <c r="X197" s="2" t="inlineStr">
+        <is>
+          <t>Ceo</t>
+        </is>
+      </c>
+      <c r="Y197" s="2" t="inlineStr"/>
+      <c r="Z197" s="2" t="inlineStr"/>
+      <c r="AA197" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/ne%C5%A1a-ktk-1757b027a/</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="2" t="inlineStr">
+        <is>
+          <t>Knjaz Milos-natura Doo Beograd</t>
+        </is>
+      </c>
+      <c r="B198" s="2" t="inlineStr">
+        <is>
+          <t>Knjaz Milos-natura Doo Beograd</t>
+        </is>
+      </c>
+      <c r="C198" s="2" t="inlineStr">
+        <is>
+          <t>122245</t>
+        </is>
+      </c>
+      <c r="D198" s="2" t="inlineStr">
+        <is>
+          <t>Serbia</t>
+        </is>
+      </c>
+      <c r="E198" s="2" t="inlineStr">
+        <is>
+          <t>Beograd</t>
+        </is>
+      </c>
+      <c r="F198" s="2" t="inlineStr">
+        <is>
+          <t>Grad Beograd</t>
+        </is>
+      </c>
+      <c r="G198" s="2" t="inlineStr">
+        <is>
+          <t>41 Bulevar Peka Dapčevića</t>
+        </is>
+      </c>
+      <c r="H198" s="2" t="inlineStr">
+        <is>
+          <t>11152</t>
+        </is>
+      </c>
+      <c r="I198" s="2" t="inlineStr">
+        <is>
+          <t>https://www.knjaznatura.co.rs</t>
+        </is>
+      </c>
+      <c r="J198" s="2" t="inlineStr"/>
+      <c r="K198" s="2" t="inlineStr"/>
+      <c r="L198" s="2" t="inlineStr">
+        <is>
+          <t>140</t>
+        </is>
+      </c>
+      <c r="M198" s="2" t="inlineStr"/>
+      <c r="N198" s="2" t="inlineStr">
+        <is>
+          <t>office@knjaznatura.co.rs</t>
+        </is>
+      </c>
+      <c r="O198" s="2" t="inlineStr">
+        <is>
+          <t>+381 800 000008</t>
+        </is>
+      </c>
+      <c r="P198" s="2" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="Q198" s="2" t="inlineStr">
+        <is>
+          <t>20350229</t>
+        </is>
+      </c>
+      <c r="R198" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/knjazmilosnatura/</t>
+        </is>
+      </c>
+      <c r="S198" s="2" t="inlineStr"/>
+      <c r="T198" s="2" t="inlineStr"/>
+      <c r="U198" s="2" t="inlineStr"/>
+      <c r="V198" s="2" t="inlineStr"/>
+      <c r="W198" s="2" t="inlineStr">
+        <is>
+          <t>Dušan Mančić</t>
+        </is>
+      </c>
+      <c r="X198" s="2" t="inlineStr">
+        <is>
+          <t>Head Of Sales</t>
+        </is>
+      </c>
+      <c r="Y198" s="2" t="inlineStr"/>
+      <c r="Z198" s="2" t="inlineStr"/>
+      <c r="AA198" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/du%C5%A1an-man%C4%8Di%C4%87-62822a46/</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="2" t="inlineStr">
+        <is>
+          <t>Knjaz Milos-natura Doo Beograd</t>
+        </is>
+      </c>
+      <c r="B199" s="2" t="inlineStr">
+        <is>
+          <t>Knjaz Milos-natura Doo Beograd</t>
+        </is>
+      </c>
+      <c r="C199" s="2" t="inlineStr">
+        <is>
+          <t>122245</t>
+        </is>
+      </c>
+      <c r="D199" s="2" t="inlineStr">
+        <is>
+          <t>Serbia</t>
+        </is>
+      </c>
+      <c r="E199" s="2" t="inlineStr">
+        <is>
+          <t>Beograd</t>
+        </is>
+      </c>
+      <c r="F199" s="2" t="inlineStr">
+        <is>
+          <t>Grad Beograd</t>
+        </is>
+      </c>
+      <c r="G199" s="2" t="inlineStr">
+        <is>
+          <t>41 Bulevar Peka Dapčevića</t>
+        </is>
+      </c>
+      <c r="H199" s="2" t="inlineStr">
+        <is>
+          <t>11152</t>
+        </is>
+      </c>
+      <c r="I199" s="2" t="inlineStr">
+        <is>
+          <t>https://www.knjaznatura.co.rs</t>
+        </is>
+      </c>
+      <c r="J199" s="2" t="inlineStr"/>
+      <c r="K199" s="2" t="inlineStr"/>
+      <c r="L199" s="2" t="inlineStr">
+        <is>
+          <t>140</t>
+        </is>
+      </c>
+      <c r="M199" s="2" t="inlineStr"/>
+      <c r="N199" s="2" t="inlineStr">
+        <is>
+          <t>office@knjaznatura.co.rs</t>
+        </is>
+      </c>
+      <c r="O199" s="2" t="inlineStr">
+        <is>
+          <t>+381 800 000008</t>
+        </is>
+      </c>
+      <c r="P199" s="2" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="Q199" s="2" t="inlineStr">
+        <is>
+          <t>20350229</t>
+        </is>
+      </c>
+      <c r="R199" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/knjazmilosnatura/</t>
+        </is>
+      </c>
+      <c r="S199" s="2" t="inlineStr"/>
+      <c r="T199" s="2" t="inlineStr"/>
+      <c r="U199" s="2" t="inlineStr"/>
+      <c r="V199" s="2" t="inlineStr"/>
+      <c r="W199" s="2" t="inlineStr">
+        <is>
+          <t>Srdjan Martic</t>
+        </is>
+      </c>
+      <c r="X199" s="2" t="inlineStr">
+        <is>
+          <t>Regional Sales Representative</t>
+        </is>
+      </c>
+      <c r="Y199" s="2" t="inlineStr"/>
+      <c r="Z199" s="2" t="inlineStr"/>
+      <c r="AA199" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/srdjan-martic-092122254/</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="2" t="inlineStr">
+        <is>
+          <t>Knjaz Milos-natura Doo Beograd</t>
+        </is>
+      </c>
+      <c r="B200" s="2" t="inlineStr">
+        <is>
+          <t>Knjaz Milos-natura Doo Beograd</t>
+        </is>
+      </c>
+      <c r="C200" s="2" t="inlineStr">
+        <is>
+          <t>122245</t>
+        </is>
+      </c>
+      <c r="D200" s="2" t="inlineStr">
+        <is>
+          <t>Serbia</t>
+        </is>
+      </c>
+      <c r="E200" s="2" t="inlineStr">
+        <is>
+          <t>Beograd</t>
+        </is>
+      </c>
+      <c r="F200" s="2" t="inlineStr">
+        <is>
+          <t>Grad Beograd</t>
+        </is>
+      </c>
+      <c r="G200" s="2" t="inlineStr">
+        <is>
+          <t>41 Bulevar Peka Dapčevića</t>
+        </is>
+      </c>
+      <c r="H200" s="2" t="inlineStr">
+        <is>
+          <t>11152</t>
+        </is>
+      </c>
+      <c r="I200" s="2" t="inlineStr">
+        <is>
+          <t>https://www.knjaznatura.co.rs</t>
+        </is>
+      </c>
+      <c r="J200" s="2" t="inlineStr"/>
+      <c r="K200" s="2" t="inlineStr"/>
+      <c r="L200" s="2" t="inlineStr">
+        <is>
+          <t>140</t>
+        </is>
+      </c>
+      <c r="M200" s="2" t="inlineStr"/>
+      <c r="N200" s="2" t="inlineStr">
+        <is>
+          <t>office@knjaznatura.co.rs</t>
+        </is>
+      </c>
+      <c r="O200" s="2" t="inlineStr">
+        <is>
+          <t>+381 800 000008</t>
+        </is>
+      </c>
+      <c r="P200" s="2" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="Q200" s="2" t="inlineStr">
+        <is>
+          <t>20350229</t>
+        </is>
+      </c>
+      <c r="R200" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/knjazmilosnatura/</t>
+        </is>
+      </c>
+      <c r="S200" s="2" t="inlineStr"/>
+      <c r="T200" s="2" t="inlineStr"/>
+      <c r="U200" s="2" t="inlineStr"/>
+      <c r="V200" s="2" t="inlineStr"/>
+      <c r="W200" s="2" t="inlineStr">
+        <is>
+          <t>Dejan Pantic</t>
+        </is>
+      </c>
+      <c r="X200" s="2" t="inlineStr">
+        <is>
+          <t>Logistics Manager</t>
+        </is>
+      </c>
+      <c r="Y200" s="2" t="inlineStr"/>
+      <c r="Z200" s="2" t="inlineStr"/>
+      <c r="AA200" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/dejan-pantic-b1750ab9/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Serbia.xlsx
+++ b/BWI/bestwine_output/bestwine_Serbia.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA200"/>
+  <dimension ref="A1:AA204"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -22008,6 +22008,410 @@
         </is>
       </c>
     </row>
+    <row r="201">
+      <c r="A201" s="2" t="inlineStr">
+        <is>
+          <t>Ktk Komerc D.o.o.</t>
+        </is>
+      </c>
+      <c r="B201" s="2" t="inlineStr">
+        <is>
+          <t>Ktk Komerc D.o.o.</t>
+        </is>
+      </c>
+      <c r="C201" s="2" t="inlineStr">
+        <is>
+          <t>146429</t>
+        </is>
+      </c>
+      <c r="D201" s="2" t="inlineStr">
+        <is>
+          <t>Serbia</t>
+        </is>
+      </c>
+      <c r="E201" s="2" t="inlineStr">
+        <is>
+          <t>Kruševac</t>
+        </is>
+      </c>
+      <c r="F201" s="2" t="inlineStr">
+        <is>
+          <t>Rasinski Okrug</t>
+        </is>
+      </c>
+      <c r="G201" s="2" t="inlineStr">
+        <is>
+          <t>81 Balkanska</t>
+        </is>
+      </c>
+      <c r="H201" s="2" t="inlineStr"/>
+      <c r="I201" s="2" t="inlineStr">
+        <is>
+          <t>https://ktkmarketi.com</t>
+        </is>
+      </c>
+      <c r="J201" s="2" t="inlineStr"/>
+      <c r="K201" s="2" t="inlineStr"/>
+      <c r="L201" s="2" t="inlineStr">
+        <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="M201" s="2" t="inlineStr"/>
+      <c r="N201" s="2" t="inlineStr">
+        <is>
+          <t>marketiktk@gmail.com</t>
+        </is>
+      </c>
+      <c r="O201" s="2" t="inlineStr">
+        <is>
+          <t>+381 37 448620</t>
+        </is>
+      </c>
+      <c r="P201" s="2" t="inlineStr">
+        <is>
+          <t>1998</t>
+        </is>
+      </c>
+      <c r="Q201" s="2" t="inlineStr">
+        <is>
+          <t>07852398</t>
+        </is>
+      </c>
+      <c r="R201" s="2" t="inlineStr"/>
+      <c r="S201" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/ktkmarketi/</t>
+        </is>
+      </c>
+      <c r="T201" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/ktk.marketi</t>
+        </is>
+      </c>
+      <c r="U201" s="2" t="inlineStr"/>
+      <c r="V201" s="2" t="inlineStr"/>
+      <c r="W201" s="2" t="inlineStr">
+        <is>
+          <t>Neša Ktk</t>
+        </is>
+      </c>
+      <c r="X201" s="2" t="inlineStr">
+        <is>
+          <t>Ceo</t>
+        </is>
+      </c>
+      <c r="Y201" s="2" t="inlineStr"/>
+      <c r="Z201" s="2" t="inlineStr"/>
+      <c r="AA201" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/ne%C5%A1a-ktk-1757b027a/</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="2" t="inlineStr">
+        <is>
+          <t>Knjaz Milos-natura Doo Beograd</t>
+        </is>
+      </c>
+      <c r="B202" s="2" t="inlineStr">
+        <is>
+          <t>Knjaz Milos-natura Doo Beograd</t>
+        </is>
+      </c>
+      <c r="C202" s="2" t="inlineStr">
+        <is>
+          <t>122245</t>
+        </is>
+      </c>
+      <c r="D202" s="2" t="inlineStr">
+        <is>
+          <t>Serbia</t>
+        </is>
+      </c>
+      <c r="E202" s="2" t="inlineStr">
+        <is>
+          <t>Beograd</t>
+        </is>
+      </c>
+      <c r="F202" s="2" t="inlineStr">
+        <is>
+          <t>Grad Beograd</t>
+        </is>
+      </c>
+      <c r="G202" s="2" t="inlineStr">
+        <is>
+          <t>41 Bulevar Peka Dapčevića</t>
+        </is>
+      </c>
+      <c r="H202" s="2" t="inlineStr">
+        <is>
+          <t>11152</t>
+        </is>
+      </c>
+      <c r="I202" s="2" t="inlineStr">
+        <is>
+          <t>https://www.knjaznatura.co.rs</t>
+        </is>
+      </c>
+      <c r="J202" s="2" t="inlineStr"/>
+      <c r="K202" s="2" t="inlineStr"/>
+      <c r="L202" s="2" t="inlineStr">
+        <is>
+          <t>140</t>
+        </is>
+      </c>
+      <c r="M202" s="2" t="inlineStr"/>
+      <c r="N202" s="2" t="inlineStr">
+        <is>
+          <t>office@knjaznatura.co.rs</t>
+        </is>
+      </c>
+      <c r="O202" s="2" t="inlineStr">
+        <is>
+          <t>+381 800 000008</t>
+        </is>
+      </c>
+      <c r="P202" s="2" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="Q202" s="2" t="inlineStr">
+        <is>
+          <t>20350229</t>
+        </is>
+      </c>
+      <c r="R202" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/knjazmilosnatura/</t>
+        </is>
+      </c>
+      <c r="S202" s="2" t="inlineStr"/>
+      <c r="T202" s="2" t="inlineStr"/>
+      <c r="U202" s="2" t="inlineStr"/>
+      <c r="V202" s="2" t="inlineStr"/>
+      <c r="W202" s="2" t="inlineStr">
+        <is>
+          <t>Dušan Mančić</t>
+        </is>
+      </c>
+      <c r="X202" s="2" t="inlineStr">
+        <is>
+          <t>Head Of Sales</t>
+        </is>
+      </c>
+      <c r="Y202" s="2" t="inlineStr"/>
+      <c r="Z202" s="2" t="inlineStr"/>
+      <c r="AA202" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/du%C5%A1an-man%C4%8Di%C4%87-62822a46/</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="2" t="inlineStr">
+        <is>
+          <t>Knjaz Milos-natura Doo Beograd</t>
+        </is>
+      </c>
+      <c r="B203" s="2" t="inlineStr">
+        <is>
+          <t>Knjaz Milos-natura Doo Beograd</t>
+        </is>
+      </c>
+      <c r="C203" s="2" t="inlineStr">
+        <is>
+          <t>122245</t>
+        </is>
+      </c>
+      <c r="D203" s="2" t="inlineStr">
+        <is>
+          <t>Serbia</t>
+        </is>
+      </c>
+      <c r="E203" s="2" t="inlineStr">
+        <is>
+          <t>Beograd</t>
+        </is>
+      </c>
+      <c r="F203" s="2" t="inlineStr">
+        <is>
+          <t>Grad Beograd</t>
+        </is>
+      </c>
+      <c r="G203" s="2" t="inlineStr">
+        <is>
+          <t>41 Bulevar Peka Dapčevića</t>
+        </is>
+      </c>
+      <c r="H203" s="2" t="inlineStr">
+        <is>
+          <t>11152</t>
+        </is>
+      </c>
+      <c r="I203" s="2" t="inlineStr">
+        <is>
+          <t>https://www.knjaznatura.co.rs</t>
+        </is>
+      </c>
+      <c r="J203" s="2" t="inlineStr"/>
+      <c r="K203" s="2" t="inlineStr"/>
+      <c r="L203" s="2" t="inlineStr">
+        <is>
+          <t>140</t>
+        </is>
+      </c>
+      <c r="M203" s="2" t="inlineStr"/>
+      <c r="N203" s="2" t="inlineStr">
+        <is>
+          <t>office@knjaznatura.co.rs</t>
+        </is>
+      </c>
+      <c r="O203" s="2" t="inlineStr">
+        <is>
+          <t>+381 800 000008</t>
+        </is>
+      </c>
+      <c r="P203" s="2" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="Q203" s="2" t="inlineStr">
+        <is>
+          <t>20350229</t>
+        </is>
+      </c>
+      <c r="R203" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/knjazmilosnatura/</t>
+        </is>
+      </c>
+      <c r="S203" s="2" t="inlineStr"/>
+      <c r="T203" s="2" t="inlineStr"/>
+      <c r="U203" s="2" t="inlineStr"/>
+      <c r="V203" s="2" t="inlineStr"/>
+      <c r="W203" s="2" t="inlineStr">
+        <is>
+          <t>Srdjan Martic</t>
+        </is>
+      </c>
+      <c r="X203" s="2" t="inlineStr">
+        <is>
+          <t>Regional Sales Representative</t>
+        </is>
+      </c>
+      <c r="Y203" s="2" t="inlineStr"/>
+      <c r="Z203" s="2" t="inlineStr"/>
+      <c r="AA203" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/srdjan-martic-092122254/</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="2" t="inlineStr">
+        <is>
+          <t>Knjaz Milos-natura Doo Beograd</t>
+        </is>
+      </c>
+      <c r="B204" s="2" t="inlineStr">
+        <is>
+          <t>Knjaz Milos-natura Doo Beograd</t>
+        </is>
+      </c>
+      <c r="C204" s="2" t="inlineStr">
+        <is>
+          <t>122245</t>
+        </is>
+      </c>
+      <c r="D204" s="2" t="inlineStr">
+        <is>
+          <t>Serbia</t>
+        </is>
+      </c>
+      <c r="E204" s="2" t="inlineStr">
+        <is>
+          <t>Beograd</t>
+        </is>
+      </c>
+      <c r="F204" s="2" t="inlineStr">
+        <is>
+          <t>Grad Beograd</t>
+        </is>
+      </c>
+      <c r="G204" s="2" t="inlineStr">
+        <is>
+          <t>41 Bulevar Peka Dapčevića</t>
+        </is>
+      </c>
+      <c r="H204" s="2" t="inlineStr">
+        <is>
+          <t>11152</t>
+        </is>
+      </c>
+      <c r="I204" s="2" t="inlineStr">
+        <is>
+          <t>https://www.knjaznatura.co.rs</t>
+        </is>
+      </c>
+      <c r="J204" s="2" t="inlineStr"/>
+      <c r="K204" s="2" t="inlineStr"/>
+      <c r="L204" s="2" t="inlineStr">
+        <is>
+          <t>140</t>
+        </is>
+      </c>
+      <c r="M204" s="2" t="inlineStr"/>
+      <c r="N204" s="2" t="inlineStr">
+        <is>
+          <t>office@knjaznatura.co.rs</t>
+        </is>
+      </c>
+      <c r="O204" s="2" t="inlineStr">
+        <is>
+          <t>+381 800 000008</t>
+        </is>
+      </c>
+      <c r="P204" s="2" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="Q204" s="2" t="inlineStr">
+        <is>
+          <t>20350229</t>
+        </is>
+      </c>
+      <c r="R204" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/knjazmilosnatura/</t>
+        </is>
+      </c>
+      <c r="S204" s="2" t="inlineStr"/>
+      <c r="T204" s="2" t="inlineStr"/>
+      <c r="U204" s="2" t="inlineStr"/>
+      <c r="V204" s="2" t="inlineStr"/>
+      <c r="W204" s="2" t="inlineStr">
+        <is>
+          <t>Dejan Pantic</t>
+        </is>
+      </c>
+      <c r="X204" s="2" t="inlineStr">
+        <is>
+          <t>Logistics Manager</t>
+        </is>
+      </c>
+      <c r="Y204" s="2" t="inlineStr"/>
+      <c r="Z204" s="2" t="inlineStr"/>
+      <c r="AA204" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/dejan-pantic-b1750ab9/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
